--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1743 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>rkXKkQTD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AqTyT2M0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>46SuSMy7</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>rcRqRtiD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dtPXTr7f</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2iXrs8a1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zRzPV4xr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EHZSUOil</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Aqipwmp8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MJflx7aE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rkHsqUUl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4rpgyREK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rZrczoUQ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>MuGorlpe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>juKJMRaR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ik4bFqh1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dt32E377</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0E9gGPxe</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>lSHwpAFr</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>MNAkH5Nl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>S0BoIo8r</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>C6QBlj7R</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dbI3Q902</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>8GUEN7pL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hQiNHHd2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>UXmi590d</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>8MoOBBNS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>jskm6koj</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>IXhBEDwA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>0drGDXhG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>AVXk7VVq</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>A7k3GZ8c</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>vsf7FgO3</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>xzDc13GK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>EanKCi8M</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>WGjaHFgi</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Eo7obhgT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>WQgDgC1p</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>p6FU1zf4</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>IJDx0EOG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>ze8saYwN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>AmNH4xAo</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>tYn8pZOT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>rsZZugXp</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>vTEY0f9A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>UBCGhWGj</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>lvML3dPi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>W2BQ2Gvb</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>b9c3oF9N</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>GQ1rjweh</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>M32viJun</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>jqfemyuB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>ATbzhaQu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>AkdSq2YI</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>CheilHP4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>p6ganefH</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>WbcOprJC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>fH0nkcAb</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>2PhKoO36</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>OYgGn4l0</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>tA4BmpZg</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>YDtwhVka</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>S607lQJm</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>4ErueStK</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>x23tzR4f</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>bHikY4Z6</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>QNqyd8RD</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>8Sbxy7kl</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>Gh2pZpK0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Uy0Yymzr</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>CKegXOlD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Yq13k64s</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>WzFyfndQ</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>OfN5tTRQ</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,760 +1042,760 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>SWX9C8ZI</t>
+          <t>632gURJ8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.55</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>vqenBDBt</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>UXmi590d</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>8MoOBBNS</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>jskm6koj</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>IXhBEDwA</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>0drGDXhG</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>AVXk7VVq</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>A7k3GZ8c</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>vsf7FgO3</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>xzDc13GK</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>EanKCi8M</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>WGjaHFgi</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Eo7obhgT</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>WQgDgC1p</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>p6FU1zf4</t>
+          <t>08pcD25G</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>IJDx0EOG</t>
+          <t>KdTaErjA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>ze8saYwN</t>
+          <t>vaq1CMKM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>AmNH4xAo</t>
+          <t>YLr5BtzT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>tYn8pZOT</t>
+          <t>rRYfhY72</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>rsZZugXp</t>
+          <t>YuRmHp6i</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.60</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>vTEY0f9A</t>
+          <t>nqViG4Lc</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2.98</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>UBCGhWGj</t>
+          <t>t6UeFOz4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>lvML3dPi</t>
+          <t>noMTBkUB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>W2BQ2Gvb</t>
+          <t>hpl1gsEp</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>b9c3oF9N</t>
+          <t>QyLXA9qI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>GQ1rjweh</t>
+          <t>Uoi8UUFe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>M32viJun</t>
+          <t>tMfCTlV1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>jqfemyuB</t>
+          <t>Wzm5h1Tj</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>ATbzhaQu</t>
+          <t>CEEHEipg</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>AkdSq2YI</t>
+          <t>4MWOCVE5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>CheilHP4</t>
+          <t>6yELDBaa</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>p6ganefH</t>
+          <t>YNFDFXUn</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>WbcOprJC</t>
+          <t>nXtecjFI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>fH0nkcAb</t>
+          <t>0zoadAUO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1805,359 +1805,6233 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2PhKoO36</t>
+          <t>EwZtLg7P</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>OYgGn4l0</t>
+          <t>GnL8GDFt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>tA4BmpZg</t>
+          <t>zPi4VA0k</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>YDtwhVka</t>
+          <t>GvBXzXxS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>S607lQJm</t>
+          <t>QHhnaCp6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>4ErueStK</t>
+          <t>Iigr0hVa</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>x23tzR4f</t>
+          <t>48ijbWaC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bHikY4Z6</t>
+          <t>dYh0Wjoq</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>QNqyd8RD</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>8Sbxy7kl</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Gh2pZpK0</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Uy0Yymzr</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>CKegXOlD</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Yq13k64s</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>WzFyfndQ</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>AkMS0VKH</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>hEBXakzO</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>6HFya9kU</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>WbNO1B5B</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>2PIK2ij5</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>lIfIy3Ui</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>UZQ75g6n</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>6gkNzNqb</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>tAUB4DLh</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>pplRZta4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>v7mVY0EA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>OYJG3Xza</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>bc9YvOXo</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>AReExqFo</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>nFu3VR7I</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>4jjbW7hC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>dO7WDaxo</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>QaifXmw6</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>dQnjYTNa</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>zBbszjgm</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>IZmnZ98g</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>fJ9e2NvP</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>M7fwyWws</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>vZmXH8wJ</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Qy97thGJ</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>4S7BuCVP</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>Y3uxBFrP</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>6LkPJU86</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>0rkTIlOC</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>zDR36Zjt</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>AgdGLjvf</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>UXmi590d</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>8MoOBBNS</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>jskm6koj</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>IXhBEDwA</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>0drGDXhG</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>AVXk7VVq</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>A7k3GZ8c</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>vsf7FgO3</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>xzDc13GK</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>EanKCi8M</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>WGjaHFgi</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Eo7obhgT</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>WQgDgC1p</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>p6FU1zf4</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>IJDx0EOG</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>ze8saYwN</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>AmNH4xAo</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>tYn8pZOT</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>rsZZugXp</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>8.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>vTEY0f9A</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>UBCGhWGj</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>lvML3dPi</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>W2BQ2Gvb</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>b9c3oF9N</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>GQ1rjweh</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>M32viJun</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>jqfemyuB</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>ATbzhaQu</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>AkdSq2YI</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>CheilHP4</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>p6ganefH</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>WbcOprJC</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>fH0nkcAb</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2PhKoO36</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>OYgGn4l0</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>tA4BmpZg</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>YDtwhVka</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>S607lQJm</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>4ErueStK</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>x23tzR4f</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>bHikY4Z6</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>QNqyd8RD</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>8Sbxy7kl</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>Gh2pZpK0</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>Uy0Yymzr</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>CKegXOlD</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>Yq13k64s</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>WzFyfndQ</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
           <t>OfN5tTRQ</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>3.85</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>IcKcrkcE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>CKJ1s9CK</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>E5m1wufk</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>MVj9yJO1</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>0MkDzwv8</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>rHDMpN1F</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>S8i5xa9e</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>v7LgqVs8</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>WtbdvLvq</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>nkKDnqX2</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>UXBUr1WR</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>M7CQqsHL</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>0hOHo3n9</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>YoWVNaf2</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>feXROuud</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>hEuyZP23</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>0vqqX3XF</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>MmpuYqI9</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>CI2lBMAd</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>bTwJQ1Aq</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>xKxNPLPk</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>ENtXZ5mc</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>r3YmWNnM</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>tliiVs2S</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>SSyDUABH</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>4hatDrtp</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>bFbpC2ej</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>nHKFVjdB</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>00I3YhCh</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>E3M7XCRb</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>IyTbZYdn</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>SCmkFVBU</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>8QLBWWt5</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>voUfzFst</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>lMloGBdO</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>fNexIXRB</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>00dYIDC5</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>7.34</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>6catHisI</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>M9cUJgca</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Qs4LLFSn</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>faDkRy5P</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>txNe5fr6</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>4Y2PKZsg</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>E3z33YCI</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>hfZ62hSO</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>WK4HMeDt</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>KSLa4EcC</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>pATn7GDg</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>bDXj6zTa</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>hCl8EbLJ</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>W2mCDIzQ</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>jmUr8dbm</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>v90QkFrJ</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>pA7HiyE6</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>CdVv9xqs</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>xp49gcqf</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>6J8DhHb0</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>bg55fwUm</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>GUF0eJEs</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>v9OYaa6Q</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>pnPU0uiK</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>W4YFmVG3</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>KU63vRwj</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>0pQWqmGS</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>plz8kini</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>AeXJnkW9</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2gCbu7Oq</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>OvZBlB1c</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>hKMOo9oG</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>6NQSpT0M</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>rqdPQ79j</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>C05gWToT</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Y96kX9WM</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>GYBpYkHG</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>UuhLRmfp</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>xrDtZV1A</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>rLDxzCn4</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>lMKTyYHi</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>UHm3LCXA</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>xriBJj2N</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>AVLPxE2o</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>WpAYzhXc</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>K6tGIAHT</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>MFSsEUPp</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>Ovm7KWnH</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>jRlaMhI4</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>O4I2NY2b</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>pEJbOEmh</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>xlGjQzJu</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>Us7RP67a</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2XbvN4iI</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>Ac2nLrMU</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>W63rMO6O</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>zL7NQnhg</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>Ot0zOpxC</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>tIAVOQM5</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>dU8JRSxm</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>jiKfPfYo</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>vgEES8Nt</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2TjopygE</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>M9ZFUegR</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>E7AjOgWf</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>zNbaMX07</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>zgX3Xc98</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>EqW7WHOE</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>lQ23LiGD</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>86VBVyvL</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>SjCrQF1r</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>6sBnPZGl</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>hb9fNDo1</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>3.45</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>trWntSE7</t>
+          <t>WdfLujx9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SvbdWyTh</t>
+          <t>h6eHtWM2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,315 +485,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AoWGqXpJ</t>
+          <t>QJgPvAiF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>hIoLKAg0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>KEflYcbt</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>EyfhXHDn</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ryEQJ8Fk</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>nTYkQAxM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>QJXgPUiS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgUoRjNF</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>xbDUISUe</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>W0AMKl0q</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>GlCYHnp2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>v3VsSW79</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dvtwTCh3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ryxZThwc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4.65</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>6.15</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,8580 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WdfLujx9</t>
+          <t>rVQsrZR4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h6eHtWM2</t>
+          <t>l8RwqFCb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>trWntSE7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SvbdWyTh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hIoLKAg0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>KEflYcbt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>EyfhXHDn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rkXKkQTD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>AqTyT2M0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>46SuSMy7</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rcRqRtiD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dtPXTr7f</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2iXrs8a1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>zRzPV4xr</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EHZSUOil</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Aqipwmp8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>MJflx7aE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>rkHsqUUl</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>4rpgyREK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>rZrczoUQ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>MuGorlpe</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>juKJMRaR</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Ik4bFqh1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>dt32E377</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>0E9gGPxe</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>lSHwpAFr</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>MNAkH5Nl</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>S0BoIo8r</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>C6QBlj7R</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>dbI3Q902</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>8GUEN7pL</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>hQiNHHd2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>632gURJ8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>p0lFJwSk</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>vNmJIcsd</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>MHXbihN8</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>69kBKJCq</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>h29zRLZF</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>QF7rPa4S</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>nP8vQukM</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>AszX60rp</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>jix3jCxF</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>h6Py6Kcj</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>WdOu5vDd</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>KCHNTNkc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>b3GRSs53</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tS5WR1K9</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>08pcD25G</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>KdTaErjA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>vaq1CMKM</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>YLr5BtzT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>rRYfhY72</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>YuRmHp6i</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>nqViG4Lc</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>t6UeFOz4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>noMTBkUB</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>hpl1gsEp</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>QyLXA9qI</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>Uoi8UUFe</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>tMfCTlV1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Wzm5h1Tj</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>CEEHEipg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>4MWOCVE5</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>6yELDBaa</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>YNFDFXUn</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>nXtecjFI</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>0zoadAUO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>EwZtLg7P</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>GnL8GDFt</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>zPi4VA0k</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>GvBXzXxS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>QHhnaCp6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Iigr0hVa</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>48ijbWaC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>dYh0Wjoq</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>AkMS0VKH</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>hEBXakzO</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>6HFya9kU</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>WbNO1B5B</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>2PIK2ij5</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>lIfIy3Ui</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>UZQ75g6n</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>6gkNzNqb</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>tAUB4DLh</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>pplRZta4</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>v7mVY0EA</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>OYJG3Xza</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>bc9YvOXo</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>AReExqFo</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>nFu3VR7I</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>4jjbW7hC</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>dO7WDaxo</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>QaifXmw6</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>dQnjYTNa</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>zBbszjgm</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>IZmnZ98g</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>fJ9e2NvP</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>M7fwyWws</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>vZmXH8wJ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Qy97thGJ</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>4S7BuCVP</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>Y3uxBFrP</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>6LkPJU86</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>0rkTIlOC</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>zDR36Zjt</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>AgdGLjvf</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>WxO8JaL6</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Kb43usrQ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>0hnWz1js</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>vqozzL5m</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>bBA1LLjf</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>xdMhNsMs</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>S4HHHwjJ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Y5pvZvLg</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>KKBcM1yl</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>hnP4Ku60</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>E1DDIJzD</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>t85atNSJ</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>WdfLujx9</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>h6eHtWM2</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
           <t>QJgPvAiF</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>4.30</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>ryEQJ8Fk</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>nTYkQAxM</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>QJXgPUiS</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>IgUoRjNF</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>xbDUISUe</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>W0AMKl0q</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>GlCYHnp2</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>v3VsSW79</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>dvtwTCh3</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>ryxZThwc</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>UXmi590d</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>8MoOBBNS</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>jskm6koj</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>IXhBEDwA</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>0drGDXhG</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>AVXk7VVq</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>A7k3GZ8c</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>vsf7FgO3</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>xzDc13GK</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>EanKCi8M</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>WGjaHFgi</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>Eo7obhgT</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>WQgDgC1p</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>p6FU1zf4</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>IJDx0EOG</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>ze8saYwN</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>AmNH4xAo</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>tYn8pZOT</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>rsZZugXp</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>5.02</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>8.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>vTEY0f9A</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>UBCGhWGj</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>lvML3dPi</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>W2BQ2Gvb</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>b9c3oF9N</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>GQ1rjweh</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>M32viJun</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>jqfemyuB</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>ATbzhaQu</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>AkdSq2YI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>CheilHP4</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>p6ganefH</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>5.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>WbcOprJC</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>fH0nkcAb</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>4.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>2PhKoO36</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>OYgGn4l0</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>tA4BmpZg</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>YDtwhVka</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>S607lQJm</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>4ErueStK</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>x23tzR4f</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>bHikY4Z6</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>QNqyd8RD</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>8Sbxy7kl</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>Gh2pZpK0</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>Uy0Yymzr</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>CKegXOlD</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>Yq13k64s</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>WzFyfndQ</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>OfN5tTRQ</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>IcKcrkcE</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>CKJ1s9CK</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>E5m1wufk</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>MVj9yJO1</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>0MkDzwv8</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>rHDMpN1F</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>S8i5xa9e</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>v7LgqVs8</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>WtbdvLvq</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>nkKDnqX2</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>4.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>UXBUr1WR</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>4.60</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>M7CQqsHL</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>0hOHo3n9</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>4.90</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>7.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>YoWVNaf2</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>feXROuud</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>hEuyZP23</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>0vqqX3XF</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>MmpuYqI9</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>CI2lBMAd</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>bTwJQ1Aq</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>xKxNPLPk</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>ENtXZ5mc</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>r3YmWNnM</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>tliiVs2S</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>SSyDUABH</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>4hatDrtp</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>bFbpC2ej</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>nHKFVjdB</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>00I3YhCh</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>E3M7XCRb</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>IyTbZYdn</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>SCmkFVBU</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>8QLBWWt5</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>voUfzFst</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>lMloGBdO</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>fNexIXRB</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>5.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>00dYIDC5</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>7.34</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>6catHisI</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>M9cUJgca</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Qs4LLFSn</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>faDkRy5P</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>txNe5fr6</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>4Y2PKZsg</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>4.45</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>7.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>E3z33YCI</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>hfZ62hSO</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>WK4HMeDt</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>KSLa4EcC</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>pATn7GDg</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>bDXj6zTa</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>hCl8EbLJ</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>W2mCDIzQ</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>jmUr8dbm</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>v90QkFrJ</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>pA7HiyE6</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>CdVv9xqs</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>xp49gcqf</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>6J8DhHb0</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>bg55fwUm</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>GUF0eJEs</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>v9OYaa6Q</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>pnPU0uiK</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>3.72</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>COgk2UVd</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>bL57wogd</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>W4YFmVG3</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>KU63vRwj</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>0pQWqmGS</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>plz8kini</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>AeXJnkW9</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2gCbu7Oq</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>OvZBlB1c</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>hKMOo9oG</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>6NQSpT0M</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>rqdPQ79j</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>C05gWToT</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>Y96kX9WM</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>GYBpYkHG</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>UuhLRmfp</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>xrDtZV1A</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>rLDxzCn4</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>lMKTyYHi</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>UHm3LCXA</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>xriBJj2N</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>AVLPxE2o</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>WpAYzhXc</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>K6tGIAHT</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>MFSsEUPp</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>Ovm7KWnH</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>jRlaMhI4</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>O4I2NY2b</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>pEJbOEmh</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>xlGjQzJu</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>Us7RP67a</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2XbvN4iI</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>Ac2nLrMU</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>W63rMO6O</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>zL7NQnhg</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>Ot0zOpxC</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>tIAVOQM5</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>dU8JRSxm</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>jiKfPfYo</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>vgEES8Nt</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2TjopygE</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>M9ZFUegR</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>E7AjOgWf</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>zNbaMX07</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>zgX3Xc98</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>EqW7WHOE</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>lQ23LiGD</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>86VBVyvL</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>SjCrQF1r</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>6sBnPZGl</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>hb9fNDo1</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>3.45</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,100 +448,100 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xhnHdYtb</t>
+          <t>bR2B69AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GroLehd4</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJuQfCBA</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rVnDcERi</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0n3Ddmal</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,151 +551,151 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SM4QZAZp</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>URr9bfCo</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QDIbviRT</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ImJfuXBN</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>dYUosgsB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U3Cs29yR</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vcKjtDdH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -705,51 +705,293 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Me49cTqr</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SYdMjeTC</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>p2PIpxK5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>vPOMqdZB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6exiWx5C</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>GQJsg0CP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Qa9Hnbkg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>hnB9lKKt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>zVteVdKI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>S4wmXIk6</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>n9ADmvzm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>6BQEoI4a</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>6.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ELuaUGZO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>3.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.80</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
+++ b/data/usa/p6_deployment/missing/data_understanding/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,56 +448,56 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR2B69AM</t>
+          <t>AwME1KOf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>E99Th5bD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>ph6YLlA9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,129 +507,129 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>UHiGG8jK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>Or5xL8PF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>4tJ63tfr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>GGMA209l</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>jRhCHlyE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>SdLZ0mYq</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,107 +639,107 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>QmZ75TPS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>MJKw07mj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>zNOsaR2d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>xS2QNAuc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>GI1UMUf3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -749,249 +749,271 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>p2PIpxK5</t>
+          <t>ID0yCpq9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.40</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.80</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vPOMqdZB</t>
+          <t>Eed8egYN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.65</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6exiWx5C</t>
+          <t>z5c4dZIH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.85</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GQJsg0CP</t>
+          <t>46dq1c4n</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.68</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Qa9Hnbkg</t>
+          <t>QFcu2wkt</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>2.98</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hnB9lKKt</t>
+          <t>pG4iayZb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>zVteVdKI</t>
+          <t>ziIVsz4O</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>S4wmXIk6</t>
+          <t>ptlrYbz0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.95</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>n9ADmvzm</t>
+          <t>EsHZtfJU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>12.50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>6BQEoI4a</t>
+          <t>nVol0HJh</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>ELuaUGZO</t>
+          <t>IT2acF3B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>hSSQrGlI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
